--- a/data/trans_dic/P56$amigo-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P56$amigo-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,41%</t>
         </is>
       </c>
     </row>
@@ -732,47 +732,47 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,59; 18,69</t>
+          <t>1,58; 21,46</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,27</t>
+          <t>0,0; 19,03</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,06</t>
+          <t>0,0; 12,11</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,12</t>
+          <t>0,0; 12,22</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,12; 10,67</t>
+          <t>1,12; 11,01</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,97</t>
+          <t>0,0; 11,7</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,01</t>
+          <t>0,0; 7,8</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,65</t>
+          <t>0,0; 9,46</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,18; 10,74</t>
+          <t>2,46; 10,64</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,2%</t>
         </is>
       </c>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,83; 22,8</t>
+          <t>2,85; 22,92</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -872,47 +872,47 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,52; 7,55</t>
+          <t>0,53; 6,88</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,85</t>
+          <t>0,0; 7,84</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,71; 6,88</t>
+          <t>0,68; 6,2</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,54</t>
+          <t>0,0; 6,51</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,03; 6,25</t>
+          <t>1,9; 5,84</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,97; 9,52</t>
+          <t>0,99; 8,83</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,5; 4,96</t>
+          <t>0,51; 5,11</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,55</t>
+          <t>0,0; 4,52</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,94; 5,3</t>
+          <t>1,74; 4,93</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,72%</t>
         </is>
       </c>
     </row>
@@ -997,7 +997,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,1; 15,05</t>
+          <t>2,1; 15,99</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1012,47 +1012,47 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,61; 8,32</t>
+          <t>1,39; 8,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,09</t>
+          <t>0,0; 7,23</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,01; 5,9</t>
+          <t>0,96; 5,8</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,57; 4,95</t>
+          <t>0,56; 4,91</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,31; 5,83</t>
+          <t>2,37; 6,12</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,39; 8,16</t>
+          <t>1,37; 7,98</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,73; 4,22</t>
+          <t>0,74; 4,18</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,4; 3,79</t>
+          <t>0,4; 3,74</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,69; 5,81</t>
+          <t>2,45; 5,58</t>
         </is>
       </c>
     </row>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2209</t>
+          <t>2335</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2363</t>
+          <t>2561</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4572</t>
+          <t>4895</t>
         </is>
       </c>
     </row>
@@ -1378,47 +1378,47 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>471; 5543</t>
+          <t>489; 6650</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 4695</t>
+          <t>0; 4199</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 5083</t>
+          <t>0; 5102</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 4991</t>
+          <t>0; 5033</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>595; 5656</t>
+          <t>665; 6544</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 3832</t>
+          <t>0; 4088</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 5092</t>
+          <t>0; 4958</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 5389</t>
+          <t>0; 5891</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1801; 8872</t>
+          <t>2221; 9621</t>
         </is>
       </c>
     </row>
@@ -1518,7 +1518,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1807</t>
+          <t>1710</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1538,7 +1538,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>7146</t>
+          <t>7679</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1558,7 +1558,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>8953</t>
+          <t>9389</t>
         </is>
       </c>
     </row>
@@ -1571,7 +1571,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1003; 8076</t>
+          <t>1009; 8116</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1586,47 +1586,47 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>377; 5463</t>
+          <t>411; 5336</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 5614</t>
+          <t>0; 5605</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1161; 11215</t>
+          <t>1105; 10111</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 8547</t>
+          <t>0; 8497</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4024; 12383</t>
+          <t>4102; 12619</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1037; 10173</t>
+          <t>1061; 9437</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1100; 10919</t>
+          <t>1119; 11258</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 8271</t>
+          <t>0; 8215</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5260; 14344</t>
+          <t>5110; 14468</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4016</t>
+          <t>4045</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9509</t>
+          <t>10239</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>13524</t>
+          <t>14284</t>
         </is>
       </c>
     </row>
@@ -1779,7 +1779,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1013; 7266</t>
+          <t>1012; 7720</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1794,47 +1794,47 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1640; 8489</t>
+          <t>1506; 8681</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 6632</t>
+          <t>0; 6763</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2069; 12115</t>
+          <t>1976; 11896</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>973; 8504</t>
+          <t>965; 8435</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5800; 14629</t>
+          <t>6525; 16865</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1978; 11567</t>
+          <t>1937; 11320</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2062; 11962</t>
+          <t>2090; 11859</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>978; 9233</t>
+          <t>977; 9130</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>9491; 20514</t>
+          <t>9414; 21425</t>
         </is>
       </c>
     </row>
